--- a/education_forms/037_school_of_nursing_grading_report_form--education_forms.xlsx
+++ b/education_forms/037_school_of_nursing_grading_report_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'quarter_1'}</t>
+          <t>quarter_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Quarter 1'}</t>
+          <t>Quarter 1</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'quarter_2'}</t>
+          <t>quarter_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Quarter 2'}</t>
+          <t>Quarter 2</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'quarter_3'}</t>
+          <t>quarter_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Quarter 3'}</t>
+          <t>Quarter 3</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'0-49'}</t>
+          <t>0-49</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '0-49'}</t>
+          <t>0-49</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'50-59'}</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '50-59'}</t>
+          <t>50-59</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'60-69'}</t>
+          <t>60-69</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '60-69'}</t>
+          <t>60-69</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'70-79'}</t>
+          <t>70-79</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': '70-79'}</t>
+          <t>70-79</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'80-89'}</t>
+          <t>80-89</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': '80-89'}</t>
+          <t>80-89</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'90-100'}</t>
+          <t>90-100</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': '90-100'}</t>
+          <t>90-100</t>
         </is>
       </c>
     </row>
